--- a/virtual-physics-lab/app/dl/ACJC_Q2_wire_circuit.xlsx
+++ b/virtual-physics-lab/app/dl/ACJC_Q2_wire_circuit.xlsx
@@ -17,8 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000E+00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -93,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -101,10 +102,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -639,7 +641,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>E = 3.08 V. Plot (E − V)/L against V.</t>
+          <t>E = 1.54 V. Plot (E − V)/L against V.</t>
         </is>
       </c>
     </row>
@@ -671,55 +673,55 @@
       <c r="A6" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="C6" s="6" t="n"/>
+      <c r="B6" s="6" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="C6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="C7" s="6" t="n"/>
+      <c r="B7" s="6" t="n">
+        <v>1.057</v>
+      </c>
+      <c r="C7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B8" s="5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="C8" s="6" t="n"/>
+      <c r="B8" s="6" t="n">
+        <v>1.018</v>
+      </c>
+      <c r="C8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="C9" s="6" t="n"/>
+      <c r="B9" s="6" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="C9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="C10" s="6" t="n"/>
+      <c r="B10" s="6" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="C10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="C11" s="6" t="n"/>
+      <c r="B11" s="6" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="C11" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -793,14 +795,14 @@
       <c r="A6" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="C6" s="7">
-        <f>(3.08-B6)/(A6/100)</f>
+      <c r="B6" s="6" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="C6" s="8">
+        <f>(1.54-B6)/(A6/100)</f>
         <v/>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>P = gradient</t>
         </is>
@@ -809,7 +811,7 @@
         <f>SLOPE(C6:C11,B6:B11)</f>
         <v/>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>m⁻¹</t>
         </is>
@@ -819,14 +821,14 @@
       <c r="A7" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="C7" s="7">
-        <f>(3.08-B7)/(A7/100)</f>
+      <c r="B7" s="6" t="n">
+        <v>1.057</v>
+      </c>
+      <c r="C7" s="8">
+        <f>(1.54-B7)/(A7/100)</f>
         <v/>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>Q = −intercept</t>
         </is>
@@ -835,7 +837,7 @@
         <f>-INTERCEPT(C6:C11,B6:B11)</f>
         <v/>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>V m⁻¹</t>
         </is>
@@ -845,14 +847,14 @@
       <c r="A8" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B8" s="5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="C8" s="7">
-        <f>(3.08-B8)/(A8/100)</f>
+      <c r="B8" s="6" t="n">
+        <v>1.018</v>
+      </c>
+      <c r="C8" s="8">
+        <f>(1.54-B8)/(A8/100)</f>
         <v/>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Q/P</t>
         </is>
@@ -861,7 +863,7 @@
         <f>-INTERCEPT(C6:C11,B6:B11)/SLOPE(C6:C11,B6:B11)</f>
         <v/>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>V</t>
         </is>
@@ -871,14 +873,14 @@
       <c r="A9" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="C9" s="7">
-        <f>(3.08-B9)/(A9/100)</f>
+      <c r="B9" s="6" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="C9" s="8">
+        <f>(1.54-B9)/(A9/100)</f>
         <v/>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>R = 2k/P (k = 20 Ω m⁻¹)</t>
         </is>
@@ -887,7 +889,7 @@
         <f>40/SLOPE(C6:C11,B6:B11)</f>
         <v/>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -897,11 +899,11 @@
       <c r="A10" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="C10" s="7">
-        <f>(3.08-B10)/(A10/100)</f>
+      <c r="B10" s="6" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="C10" s="8">
+        <f>(1.54-B10)/(A10/100)</f>
         <v/>
       </c>
     </row>
@@ -909,11 +911,11 @@
       <c r="A11" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="C11" s="7">
-        <f>(3.08-B11)/(A11/100)</f>
+      <c r="B11" s="6" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="C11" s="8">
+        <f>(1.54-B11)/(A11/100)</f>
         <v/>
       </c>
     </row>
